--- a/tests/data/testTopology_PATH_expected.xlsx
+++ b/tests/data/testTopology_PATH_expected.xlsx
@@ -453,8 +453,8 @@
         <is>
           <t xml:space="preserve">Transceiver trx Vannes_KBE
 	- GSNR(0.1nm):: 30.84 dB
-	- GSNR(signal bw):: 26.75 dB
-	- OSNR ASE (0.1nm):: 30.84 dB
+	- GSNR(signal bw):: 26.76 dB
+	- OSNR ASE (0.1nm):: 30.85 dB
 	- OSNR ASE(signal bw):: 26.76 dB
 	- CD:: 167.00 ps/nm
 	- PMD:: 0.13 ps
@@ -519,8 +519,8 @@
           <t xml:space="preserve">Edfa east edfa in Brest_KLA to Morlaix
 	- Type: test_fixed_gain
 	- Effective_gain (before att_in and before output VOA): 21.0 dB
-	- P in: -0.223 dBm
-	- P out: 20.783 dBm
+	- P in: -0.177 dBm
+	- P out: 20.828 dBm
 	- P out/ch: 1.01 dBm
 	- NF: 5.0 dB
 	- Out VOA: 0 dB
@@ -569,8 +569,8 @@
           <t xml:space="preserve">Edfa west edfa in Lannion_CAS to Morlaix
 	- Type: std_low_gain
 	- Effective_gain (before att_in and before output VOA): 16.0 dB
-	- P in: 4.783 dBm
-	- P out: 20.786 dBm
+	- P in: 4.828 dBm
+	- P out: 20.831 dBm
 	- P out/ch: 1.01 dBm
 	- NF: 7.0 dB
 	- Out VOA: 0 dB
@@ -591,8 +591,8 @@
           <t xml:space="preserve">Edfa east edfa in Lannion_CAS to Corlay
 	- Type: test
 	- Effective_gain (before att_in and before output VOA): 21.0 dB
-	- P in: -0.223 dBm
-	- P out: 20.785 dBm
+	- P in: -0.177 dBm
+	- P out: 20.83 dBm
 	- P out/ch: 1.01 dBm
 	- NF: 6.16 dB
 	- Out VOA: 0 dB
@@ -662,8 +662,8 @@
           <t xml:space="preserve">Edfa west edfa in Lorient_KMA to Loudeac
 	- Type: std_medium_gain
 	- Effective_gain (before att_in and before output VOA): 28.0 dB
-	- P in: -7.215 dBm
-	- P out: 20.82 dBm
+	- P in: -7.17 dBm
+	- P out: 20.865 dBm
 	- P out/ch: 1.04 dBm
 	- NF: 5.98 dB
 	- Out VOA: 0 dB
@@ -684,8 +684,8 @@
           <t xml:space="preserve">Edfa east edfa in Lorient_KMA to Vannes_KBE
 	- Type: test_fixed_gain
 	- Effective_gain (before att_in and before output VOA): 21.0 dB
-	- P in: -0.223 dBm
-	- P out: 20.783 dBm
+	- P in: -0.177 dBm
+	- P out: 20.828 dBm
 	- P out/ch: 1.01 dBm
 	- NF: 5.0 dB
 	- Out VOA: 0 dB
@@ -713,8 +713,8 @@
           <t xml:space="preserve">Edfa west edfa in Vannes_KBE to Lorient_KMA
 	- Type: std_low_gain
 	- Effective_gain (before att_in and before output VOA): 10.0 dB
-	- P in: 10.783 dBm
-	- P out: 20.784 dBm
+	- P in: 10.828 dBm
+	- P out: 20.829 dBm
 	- P out/ch: 1.01 dBm
 	- NF: 8.98 dB
 	- Out VOA: 0 dB
@@ -945,8 +945,8 @@
           <t xml:space="preserve">Edfa east edfa in Rennes_STA to Ploermel
 	- Type: test_fixed_gain
 	- Effective_gain (before att_in and before output VOA): 20.0 dB
-	- P in: -2.007 dBm
-	- P out: 18.005 dBm
+	- P in: -1.938 dBm
+	- P out: 18.073 dBm
 	- P out/ch: 0.01 dBm
 	- NF: 5.0 dB
 	- Out VOA: 0 dB
@@ -974,8 +974,8 @@
           <t xml:space="preserve">Edfa east edfa in Ploermel to Vannes_KBE
 	- Type: std_low_gain
 	- Effective_gain (before att_in and before output VOA): 11.0 dB
-	- P in: 7.005 dBm
-	- P out: 18.008 dBm
+	- P in: 7.073 dBm
+	- P out: 18.076 dBm
 	- P out/ch: 0.01 dBm
 	- NF: 8.31 dB
 	- Out VOA: 0 dB
@@ -1003,8 +1003,8 @@
           <t xml:space="preserve">Edfa west edfa in Vannes_KBE to Ploermel
 	- Type: std_low_gain
 	- Effective_gain (before att_in and before output VOA): 10.0 dB
-	- P in: 8.008 dBm
-	- P out: 18.011 dBm
+	- P in: 8.076 dBm
+	- P out: 18.079 dBm
 	- P out/ch: 0.02 dBm
 	- NF: 8.98 dB
 	- Out VOA: 0 dB
@@ -1025,8 +1025,8 @@
           <t xml:space="preserve">Edfa east edfa in Vannes_KBE to Lorient_KMA
 	- Type: test_fixed_gain
 	- Effective_gain (before att_in and before output VOA): 20.0 dB
-	- P in: -2.007 dBm
-	- P out: 18.005 dBm
+	- P in: -1.938 dBm
+	- P out: 18.073 dBm
 	- P out/ch: 0.01 dBm
 	- NF: 5.0 dB
 	- Out VOA: 0 dB
@@ -1054,8 +1054,8 @@
           <t xml:space="preserve">Edfa west edfa in Lorient_KMA to Vannes_KBE
 	- Type: std_low_gain
 	- Effective_gain (before att_in and before output VOA): 10.0 dB
-	- P in: 8.005 dBm
-	- P out: 18.007 dBm
+	- P in: 8.073 dBm
+	- P out: 18.076 dBm
 	- P out/ch: 0.01 dBm
 	- NF: 8.98 dB
 	- Out VOA: 0 dB
@@ -1076,8 +1076,8 @@
           <t xml:space="preserve">Edfa east edfa in Lorient_KMA to Loudeac
 	- Type: test_fixed_gain
 	- Effective_gain (before att_in and before output VOA): 20.0 dB
-	- P in: -2.007 dBm
-	- P out: 18.005 dBm
+	- P in: -1.938 dBm
+	- P out: 18.073 dBm
 	- P out/ch: 0.01 dBm
 	- NF: 5.0 dB
 	- Out VOA: 0 dB
@@ -1147,8 +1147,8 @@
           <t xml:space="preserve">Edfa west edfa in Lannion_CAS to Corlay
 	- Type: test
 	- Effective_gain (before att_in and before output VOA): 28.0 dB
-	- P in: -9.995 dBm
-	- P out: 18.089 dBm
+	- P in: -9.927 dBm
+	- P out: 18.157 dBm
 	- P out/ch: 0.10 dBm
 	- NF: 5.76 dB
 	- Out VOA: 0 dB
@@ -1197,7 +1197,7 @@
     <row r="19" s="1" customFormat="1" ht="18" customHeight="1">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>snr@0.1nm : 28.74 dB</t>
+          <t>snr@0.1nm : 28.75 dB</t>
         </is>
       </c>
       <c r="B19" s="1" t="inlineStr">
@@ -1312,7 +1312,7 @@
       <c r="I20" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Transceiver trx Lannion_CAS
-	- GSNR(0.1nm):: 28.74 dB
+	- GSNR(0.1nm):: 28.75 dB
 	- GSNR(signal bw):: 21.65 dB
 	- OSNR ASE (0.1nm):: 30.79 dB
 	- OSNR ASE(signal bw):: 23.70 dB

--- a/tests/data/testTopology_PATH_expected.xlsx
+++ b/tests/data/testTopology_PATH_expected.xlsx
@@ -375,7 +375,7 @@
         </is>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="198" customHeight="1">
+    <row r="4" s="1" customFormat="1" ht="252" customHeight="1">
       <c r="A4" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Transceiver trx Lorient_KMA
@@ -388,6 +388,9 @@
 	- PDL:: 0.00 dB
 	- Latency: 0.0 ms
 	- Actual pch out:: 0.00 dBm
+	- CD penalty: None dB
+	- PMD penalty:: None dB
+	- PDL penalty:: None dB
 </t>
         </is>
       </c>
@@ -461,6 +464,9 @@
 	- PDL:: 0.00 dB
 	- Latency: 0.05 ms
 	- Actual pch out:: 0.00 dBm
+	- CD penalty: None dB
+	- PMD penalty:: None dB
+	- PDL penalty:: None dB
 </t>
         </is>
       </c>
@@ -491,7 +497,7 @@
         </is>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" ht="198" customHeight="1">
+    <row r="8" s="1" customFormat="1" ht="252" customHeight="1">
       <c r="A8" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Transceiver trx Brest_KLA
@@ -504,6 +510,9 @@
 	- PDL:: 0.00 dB
 	- Latency: 0.0 ms
 	- Actual pch out:: 0.00 dBm
+	- CD penalty: None dB
+	- PMD penalty:: None dB
+	- PDL penalty:: None dB
 </t>
         </is>
       </c>
@@ -742,6 +751,9 @@
 	- PDL:: 0.00 dB
 	- Latency: 1.05 ms
 	- Actual pch out:: 0.00 dBm
+	- CD penalty: None dB
+	- PMD penalty:: None dB
+	- PDL penalty:: None dB
 </t>
         </is>
       </c>
@@ -772,7 +784,7 @@
         </is>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" ht="198" customHeight="1">
+    <row r="12" s="1" customFormat="1" ht="252" customHeight="1">
       <c r="A12" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Transceiver trx Lannion_CAS
@@ -785,6 +797,9 @@
 	- PDL:: 0.00 dB
 	- Latency: 0.0 ms
 	- Actual pch out:: 0.00 dBm
+	- CD penalty: None dB
+	- PMD penalty:: None dB
+	- PDL penalty:: None dB
 </t>
         </is>
       </c>
@@ -887,6 +902,9 @@
 	- PDL:: 0.00 dB
 	- Latency: 0.61 ms
 	- Actual pch out:: 0.00 dBm
+	- CD penalty: None dB
+	- PMD penalty:: None dB
+	- PDL penalty:: None dB
 </t>
         </is>
       </c>
@@ -917,7 +935,7 @@
         </is>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" ht="198" customHeight="1">
+    <row r="16" s="1" customFormat="1" ht="252" customHeight="1">
       <c r="A16" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Transceiver trx Rennes_STA
@@ -930,6 +948,9 @@
 	- PDL:: 0.00 dB
 	- Latency: 0.0 ms
 	- Actual pch out:: 0.00 dBm
+	- CD penalty: None dB
+	- PMD penalty:: None dB
+	- PDL penalty:: None dB
 </t>
         </is>
       </c>
@@ -1176,6 +1197,9 @@
 	- PDL:: 0.00 dB
 	- Latency: 1.2 ms
 	- Actual pch out:: 0.00 dBm
+	- CD penalty: None dB
+	- PMD penalty:: None dB
+	- PDL penalty:: None dB
 </t>
         </is>
       </c>
@@ -1206,7 +1230,7 @@
         </is>
       </c>
     </row>
-    <row r="20" s="1" customFormat="1" ht="198" customHeight="1">
+    <row r="20" s="1" customFormat="1" ht="252" customHeight="1">
       <c r="A20" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Transceiver trx Rennes_STA
@@ -1219,6 +1243,9 @@
 	- PDL:: 0.00 dB
 	- Latency: 0.0 ms
 	- Actual pch out:: 0.00 dBm
+	- CD penalty: None dB
+	- PMD penalty:: None dB
+	- PDL penalty:: None dB
 </t>
         </is>
       </c>
@@ -1321,6 +1348,9 @@
 	- PDL:: 0.00 dB
 	- Latency: 0.61 ms
 	- Actual pch out:: 0.00 dBm
+	- CD penalty: None dB
+	- PMD penalty:: None dB
+	- PDL penalty:: None dB
 </t>
         </is>
       </c>

--- a/tests/data/testTopology_PATH_expected.xlsx
+++ b/tests/data/testTopology_PATH_expected.xlsx
@@ -388,9 +388,6 @@
 	- PDL:: 0.00 dB
 	- Latency: 0.0 ms
 	- Actual pch out:: 0.00 dBm
-	- CD penalty: None dB
-	- PMD penalty:: None dB
-	- PDL penalty:: None dB
 </t>
         </is>
       </c>
@@ -510,9 +507,6 @@
 	- PDL:: 0.00 dB
 	- Latency: 0.0 ms
 	- Actual pch out:: 0.00 dBm
-	- CD penalty: None dB
-	- PMD penalty:: None dB
-	- PDL penalty:: None dB
 </t>
         </is>
       </c>
@@ -797,9 +791,6 @@
 	- PDL:: 0.00 dB
 	- Latency: 0.0 ms
 	- Actual pch out:: 0.00 dBm
-	- CD penalty: None dB
-	- PMD penalty:: None dB
-	- PDL penalty:: None dB
 </t>
         </is>
       </c>
@@ -948,9 +939,6 @@
 	- PDL:: 0.00 dB
 	- Latency: 0.0 ms
 	- Actual pch out:: 0.00 dBm
-	- CD penalty: None dB
-	- PMD penalty:: None dB
-	- PDL penalty:: None dB
 </t>
         </is>
       </c>
@@ -1243,9 +1231,6 @@
 	- PDL:: 0.00 dB
 	- Latency: 0.0 ms
 	- Actual pch out:: 0.00 dBm
-	- CD penalty: None dB
-	- PMD penalty:: None dB
-	- PDL penalty:: None dB
 </t>
         </is>
       </c>
